--- a/Copolymerisation/Messwerte/Mappe1.xlsx
+++ b/Copolymerisation/Messwerte/Mappe1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dokumente\Uni laptop\Chemie\Poly\Copolymerisation\Messwerte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7CA6B11B-037B-4989-BFC1-0AC7C050DE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104757D6-45DB-4F5B-892F-9AED20CFE87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="2505" windowWidth="15765" windowHeight="12015" xr2:uid="{EC9A12D4-FC17-4DF3-91C2-7490D74CCC1E}"/>
+    <workbookView xWindow="11805" yWindow="1980" windowWidth="15765" windowHeight="12015" xr2:uid="{EC9A12D4-FC17-4DF3-91C2-7490D74CCC1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Probe</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>Initiator einwage in mg</t>
+  </si>
+  <si>
+    <t>Delta M</t>
+  </si>
+  <si>
+    <t>n_St Anfang</t>
+  </si>
+  <si>
+    <t>v_Br</t>
   </si>
 </sst>
 </file>
@@ -429,13 +438,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E9289F-E3E9-4E4D-BE1F-9BBD6364599B}">
-  <dimension ref="A2:G5"/>
+  <dimension ref="A2:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -457,13 +468,23 @@
       <c r="G2" t="s">
         <v>5</v>
       </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="1">
         <v>2.6</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C4" si="0">((B3*0.001)/164.21)/0.01</f>
+        <v>1.5833384081359234E-3</v>
       </c>
       <c r="D3">
         <v>0.32</v>
@@ -480,51 +501,94 @@
         <f>(D3/9.1)*100%</f>
         <v>3.5164835164835165E-2</v>
       </c>
+      <c r="H3">
+        <f>($B$20-F3)/0.01</f>
+        <v>0.30724915986557882</v>
+      </c>
+      <c r="I3">
+        <f>H3/7200</f>
+        <v>4.2673494425774834E-5</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>10.1</v>
       </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>6.1506607392972402E-3</v>
+      </c>
       <c r="D4">
         <v>0.63</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E5" si="0" xml:space="preserve"> 9.1*(1-G4)</f>
+        <f t="shared" ref="E4:E5" si="1" xml:space="preserve"> 9.1*(1-G4)</f>
         <v>8.4700000000000006</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F5" si="1">E4/104.15</f>
+        <f t="shared" ref="F4:F5" si="2">E4/104.15</f>
         <v>8.1325012001920313E-2</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G5" si="2">(D4/9.1)*100%</f>
+        <f t="shared" ref="G4:G5" si="3">(D4/9.1)*100%</f>
         <v>6.9230769230769235E-2</v>
       </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H5" si="4">($B$20-F4)/0.01</f>
+        <v>0.60489678348535636</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I5" si="5">H4/7200</f>
+        <v>8.4013442150743939E-5</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>24.6</v>
       </c>
+      <c r="C5">
+        <f>((B5*0.001)/164.21)/0.01</f>
+        <v>1.4980817246209121E-2</v>
+      </c>
       <c r="D5">
         <v>0.93</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.17</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.8444551128180509E-2</v>
       </c>
       <c r="G5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.10219780219780221</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="4"/>
+        <v>0.89294287085933677</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="5"/>
+        <v>1.2401984317490788E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f>9.1/104.15</f>
+        <v>8.7373979836773877E-2</v>
       </c>
     </row>
   </sheetData>
